--- a/data/Costa_Rica/output/resultados_lote_029_CR.xlsx
+++ b/data/Costa_Rica/output/resultados_lote_029_CR.xlsx
@@ -1717,11 +1717,11 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>BAJA</t>
+          <t>NO_ENCONTRADO</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1729,26 +1729,10 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>https://it.linkedin.com/in/mar%C3%ADa-betancourt-6797aa80|60</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>NO/DUDOSO</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>NO COINCIDE</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>502100317</t>
@@ -2439,7 +2423,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://cr.linkedin.com/in/jose-arrieta-20b708280|80 ; https://cr.linkedin.com/in/jose-arrieta-4b05137a|80 ; https://co.linkedin.com/in/jose-arrieta-narvaez-96195051|60</t>
+          <t>https://cr.linkedin.com/in/jose-arrieta-20b708280|80 ; https://cr.linkedin.com/in/jose-arrieta-4b05137a|80</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3205,7 +3189,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://pa.linkedin.com/in/sara-sanchez-556b9881|80 ; https://www.linkedin.com/in/sara-sanchez|80 ; https://cr.linkedin.com/in/maria-sanchez-4061b3122|80</t>
+          <t>https://pa.linkedin.com/in/sara-sanchez-556b9881|80 ; https://www.linkedin.com/in/sara-sanchez|80 ; https://pa.linkedin.com/in/mar%C3%ADa-sanchez-a9b0992a4|80</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4573,7 +4557,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://cr.linkedin.com/in/diana-maria-jimenez-ramirez-204154172|100 ; https://www.linkedin.com/in/maria-jim%C3%A9nez-msw-192364176|83 ; https://cr.linkedin.com/in/mar%C3%ADa-jim%C3%A9nez-a169a650/en|83</t>
+          <t>https://cr.linkedin.com/in/diana-maria-jimenez-ramirez-204154172|100 ; https://cr.linkedin.com/in/mar%C3%ADa-jim%C3%A9nez-a169a650/en|83 ; https://cr.linkedin.com/in/mar%C3%ADa-vargas-jim%C3%A9nez-73b63b196|83</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -7651,7 +7635,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>https://mx.linkedin.com/in/miriam-p%C3%A9rez-6482a6200|75 ; https://cr.linkedin.com/in/miriam-p%C3%A9rez-carrillo-093715109|75 ; https://www.linkedin.com/in/miriam-rodriguez-8a9093231|60</t>
+          <t>https://www.linkedin.com/in/miriam-perez-96b37749|75 ; https://mx.linkedin.com/in/miriam-p%C3%A9rez-6482a6200|75 ; https://cr.linkedin.com/in/miriam-p%C3%A9rez-carrillo-093715109|75</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8309,7 +8293,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://pa.linkedin.com/in/alexis-g%C3%B3mez-722a8813b</t>
         </is>
       </c>
       <c r="H118" t="n">
@@ -8327,7 +8311,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>https://pa.linkedin.com/in/alexis-gomez-8b7a01272|80 ; https://pa.linkedin.com/in/alexis-g%C3%B3mez-722a8813b|80</t>
+          <t>https://pa.linkedin.com/in/alexis-g%C3%B3mez-722a8813b|80 ; https://pa.linkedin.com/in/alexis-gomez-8b7a01272|80</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8829,7 +8813,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>https://cr.linkedin.com/in/roxana-morales-0756aa144|80 ; https://cr.linkedin.com/in/maria-laura-morales-a753b0337/en|80 ; https://cr.linkedin.com/in/maria-morales-49104a220|80</t>
+          <t>https://cr.linkedin.com/in/roxana-morales-0756aa144|80 ; https://cr.linkedin.com/in/maria-laura-morales-a753b0337/en|80 ; https://cr.linkedin.com/in/maria-morales-1b3b9a375|80</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -13885,7 +13869,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://mx.linkedin.com/in/gerardo-soto-92a34725</t>
         </is>
       </c>
       <c r="H202" t="n">
@@ -13903,7 +13887,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>https://cr.linkedin.com/in/gustavo-soto-a7108116|80 ; https://cr.linkedin.com/in/gustavo-soto-maroto-832ab612|80 ; https://cr.linkedin.com/in/gerardo-chavarria-salas-31692280|75</t>
+          <t>https://mx.linkedin.com/in/gerardo-soto-92a34725|80 ; https://cr.linkedin.com/in/gustavo-soto-a7108116|80 ; https://cr.linkedin.com/in/gustavo-soto-maroto-832ab612|80</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -14107,7 +14091,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/gerardo-brenes</t>
         </is>
       </c>
       <c r="H205" t="n">
@@ -14125,7 +14109,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>https://cr.linkedin.com/in/gerardo-brenes-7a7215140|80 ; https://cr.linkedin.com/in/gerardo-brenes|80 ; https://www.linkedin.com/in/hugo-brenes-83919b18|80</t>
+          <t>https://cr.linkedin.com/in/gerardo-brenes|80 ; https://cr.linkedin.com/in/gerardo-brenes-7a7215140|80 ; https://www.linkedin.com/in/hugo-brenes-83919b18|80</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -14199,7 +14183,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>https://cr.linkedin.com/in/gerardo-brenes-7a7215140|83 ; https://cr.linkedin.com/in/gerardo-brenes|83 ; https://www.linkedin.com/in/hugo-brenes-83919b18|80</t>
+          <t>https://cr.linkedin.com/in/gerardo-brenes|83 ; https://cr.linkedin.com/in/gerardo-brenes-7a7215140|83 ; https://www.linkedin.com/in/hugo-brenes-83919b18|80</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -17837,7 +17821,7 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>https://es.linkedin.com/in/elena-diaz-alvarez/es|86 ; https://pa.linkedin.com/in/silvia-alvarez-23718b278|80</t>
+          <t>https://es.linkedin.com/in/elena-diaz-alvarez/es|86 ; https://pa.linkedin.com/in/silvia-alvarez-23718b278|80 ; https://es.linkedin.com/in/silvia-alvarez-55644920|80</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -21713,7 +21697,7 @@
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>https://cr.linkedin.com/in/ivette-fernandez-moreno-800b3a157|100 ; https://cr.linkedin.com/in/ivette-fernandez-42388449|80</t>
+          <t>https://cr.linkedin.com/in/ivette-fernandez-moreno-800b3a157|100 ; https://cr.linkedin.com/in/ivette-fernandez-42388449|80 ; https://cr.linkedin.com/in/ivette-fern%C3%A1ndez-043b0179|80</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
@@ -26249,7 +26233,7 @@
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>https://mx.linkedin.com/in/mariela-vargas-95981926|83 ; https://cr.linkedin.com/in/mariela-vargas-arce-1856911b1|80 ; https://cl.linkedin.com/in/mariela-vargas-troncoso-31405735a|80</t>
+          <t>https://mx.linkedin.com/in/mariela-vargas-95981926|83 ; https://cl.linkedin.com/in/mariela-vargas-troncoso-31405735a|80 ; https://cr.linkedin.com/in/mariela-vargas-arce-1856911b1|80</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
@@ -28815,7 +28799,7 @@
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>https://cr.linkedin.com/in/alejandra-sol%C3%B3rzano-ugalde-01051515|80 ; https://cr.linkedin.com/in/alejandra-rodr%C3%ADguez-900044126|75 ; https://cr.linkedin.com/in/alejandra-rodr%C3%ADguez-arce-0b446411b|75</t>
+          <t>https://cr.linkedin.com/in/alejandra-sol%C3%B3rzano-ugalde-01051515|80 ; https://cr.linkedin.com/in/alejandra-rodr%C3%ADguez-arce-0b446411b|75 ; https://cr.linkedin.com/in/alejandra-rodr%C3%ADguez-900044126|75</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
@@ -34327,7 +34311,7 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/cristina-brice%C3%B1o/es</t>
         </is>
       </c>
       <c r="H507" t="n">
@@ -34340,12 +34324,12 @@
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
+          <t>ESTUDIÓ</t>
         </is>
       </c>
       <c r="K507" t="inlineStr">
         <is>
-          <t>https://cr.linkedin.com/in/cristina-brice%C3%B1o-74693b180|80 ; https://cr.linkedin.com/in/cristina-brice%C3%B1o/es|80</t>
+          <t>https://cr.linkedin.com/in/cristina-brice%C3%B1o/es|80 ; https://cr.linkedin.com/in/cristina-brice%C3%B1o-74693b180|80</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
@@ -38961,7 +38945,7 @@
       </c>
       <c r="K575" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jessica-castro-b50b062b|60</t>
+          <t>https://www.linkedin.com/in/jessica-castro-b50b062b|60 ; https://cr.linkedin.com/in/jessica-castro-alvarez-19ab30aa|60</t>
         </is>
       </c>
       <c r="L575" t="inlineStr">
@@ -39035,7 +39019,7 @@
       </c>
       <c r="K576" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jessica-castro-b50b062b|60</t>
+          <t>https://www.linkedin.com/in/jessica-castro-b50b062b|60 ; https://cr.linkedin.com/in/jessica-castro-alvarez-19ab30aa|60</t>
         </is>
       </c>
       <c r="L576" t="inlineStr">
@@ -40017,7 +40001,7 @@
       </c>
       <c r="K591" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/in/ana-jim%C3%A9nez-008154278|80 ; https://cr.linkedin.com/in/ana-jim%C3%A9nez-64413a12a|80 ; https://cr.linkedin.com/in/ana-jimenez-855279b4|80</t>
+          <t>https://ca.linkedin.com/in/ana-jim%C3%A9nez-008154278|80 ; https://cr.linkedin.com/in/ana-jim%C3%A9nez-64413a12a|80 ; https://cr.linkedin.com/in/ana-jimenez-8a6a8169|80</t>
         </is>
       </c>
       <c r="L591" t="inlineStr">
@@ -40091,7 +40075,7 @@
       </c>
       <c r="K592" t="inlineStr">
         <is>
-          <t>https://ca.linkedin.com/in/ana-jim%C3%A9nez-008154278|83 ; https://cr.linkedin.com/in/ana-jim%C3%A9nez-64413a12a|83 ; https://cr.linkedin.com/in/ana-jimenez-855279b4|83</t>
+          <t>https://ca.linkedin.com/in/ana-jim%C3%A9nez-008154278|83 ; https://cr.linkedin.com/in/ana-jim%C3%A9nez-64413a12a|83 ; https://cr.linkedin.com/in/ana-jimenez-8a6a8169|83</t>
         </is>
       </c>
       <c r="L592" t="inlineStr">
@@ -41427,7 +41411,7 @@
       </c>
       <c r="K612" t="inlineStr">
         <is>
-          <t>https://pa.linkedin.com/in/daniel-padilla-95a8711bb|80 ; https://pl.linkedin.com/in/daniel-padilla-68484aa|80 ; https://co.linkedin.com/in/daniel-padilla-torres|80</t>
+          <t>https://pl.linkedin.com/in/daniel-padilla-68484aa/es|83 ; https://pa.linkedin.com/in/daniel-padilla-95a8711bb|80 ; https://pl.linkedin.com/in/daniel-padilla-68484aa|80</t>
         </is>
       </c>
       <c r="L612" t="inlineStr">
@@ -42029,7 +42013,7 @@
       </c>
       <c r="K621" t="inlineStr">
         <is>
-          <t>https://cr.linkedin.com/in/johanna-l%C3%B3pez-kikut-383b42120/en|75 ; https://cr.linkedin.com/in/johanna-l%C3%B3pez-kikut-383b42120|75</t>
+          <t>https://cr.linkedin.com/in/johanna-l%C3%B3pez-kikut-383b42120/en|75 ; https://www.linkedin.com/in/johanna-l%C3%B3pez-encalada-a30830124|75 ; https://cr.linkedin.com/in/johanna-l%C3%B3pez-kikut-383b42120|75</t>
         </is>
       </c>
       <c r="L621" t="inlineStr">
@@ -42699,7 +42683,7 @@
       </c>
       <c r="K632" t="inlineStr">
         <is>
-          <t>https://cr.linkedin.com/in/francisca-mar%C3%ADa-hern%C3%A1ndez-mu%C3%B1oz-811299129|100 ; https://www.linkedin.com/in/maria-hernandez-a256781a1|80 ; https://pa.linkedin.com/in/mar%C3%ADa-hernandez-736391252|80</t>
+          <t>https://cr.linkedin.com/in/francisca-mar%C3%ADa-hern%C3%A1ndez-mu%C3%B1oz-811299129|100 ; https://pa.linkedin.com/in/mar%C3%ADa-hernandez-736391252|80 ; https://www.linkedin.com/in/maria-hernandez-b41861339|80</t>
         </is>
       </c>
       <c r="L632" t="inlineStr">
@@ -44357,7 +44341,7 @@
       </c>
       <c r="K657" t="inlineStr">
         <is>
-          <t>https://mx.linkedin.com/in/enrique-gonz%C3%A1lez-sol%C3%B3rzano-3b780aa|86 ; https://mx.linkedin.com/in/humberto-gonz%C3%A1lez-villarreal-816912159|80 ; https://pa.linkedin.com/in/carlos-humberto-gonz%C3%A1lez-4673991b7|80</t>
+          <t>https://mx.linkedin.com/in/enrique-gonz%C3%A1lez-sol%C3%B3rzano-3b780aa|86 ; https://pa.linkedin.com/in/carlos-humberto-gonz%C3%A1lez-4673991b7|80 ; https://mx.linkedin.com/in/humberto-gonz%C3%A1lez-camacho-024484159|80</t>
         </is>
       </c>
       <c r="L657" t="inlineStr">
@@ -44487,7 +44471,7 @@
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/ana-alvarez-mendez-77a6331b6</t>
         </is>
       </c>
       <c r="H659" t="n">
@@ -44505,7 +44489,7 @@
       </c>
       <c r="K659" t="inlineStr">
         <is>
-          <t>https://cr.linkedin.com/in/ana-alvarez-8248a831|80 ; https://cr.linkedin.com/in/ana-alvarez-mendez-77a6331b6|80 ; https://cr.linkedin.com/in/ana-alvarez-zarnowski-673b4a33|80</t>
+          <t>https://cr.linkedin.com/in/ana-alvarez-mendez-77a6331b6|80 ; https://cr.linkedin.com/in/ana-alvarez-8248a831|80 ; https://cr.linkedin.com/in/ana-alvarez-zarnowski-673b4a33|80</t>
         </is>
       </c>
       <c r="L659" t="inlineStr">
@@ -45289,15 +45273,15 @@
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://pe.linkedin.com/in/wendy-garcia-207610196</t>
         </is>
       </c>
       <c r="H672" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J672" t="inlineStr">
@@ -45305,10 +45289,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
-      <c r="L672" t="inlineStr"/>
-      <c r="M672" t="inlineStr"/>
-      <c r="N672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>https://pe.linkedin.com/in/wendy-garcia-207610196|86</t>
+        </is>
+      </c>
+      <c r="L672" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M672" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N672" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O672" t="inlineStr">
         <is>
           <t>503330035</t>
@@ -46971,7 +46971,7 @@
       </c>
       <c r="K696" t="inlineStr">
         <is>
-          <t>https://ec.linkedin.com/in/patricia-miranda-55a09146|80 ; https://cl.linkedin.com/in/patricia-miranda-miskin|80</t>
+          <t>https://ec.linkedin.com/in/patricia-miranda-55a09146|80</t>
         </is>
       </c>
       <c r="L696" t="inlineStr">
@@ -48233,7 +48233,7 @@
       </c>
       <c r="K715" t="inlineStr">
         <is>
-          <t>https://cr.linkedin.com/in/luis-mora-072417210|80 ; https://cr.linkedin.com/in/luis-mora-3291b7169|80 ; https://www.linkedin.com/in/luis-mora-arias-616b86140|80</t>
+          <t>https://cr.linkedin.com/in/luis-mora-072417210|80 ; https://www.linkedin.com/in/luis-mora-arias-616b86140|80 ; https://cr.linkedin.com/in/luis-mora-3291b7169|80</t>
         </is>
       </c>
       <c r="L715" t="inlineStr">
@@ -49179,7 +49179,7 @@
       </c>
       <c r="K728" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/vanessa-salazar-a7a3701|80 ; https://cr.linkedin.com/in/vanessa-salazar-25777410a|80 ; https://cr.linkedin.com/in/vanessa-salazar-rosales-01890040|80</t>
+          <t>https://www.linkedin.com/in/vanessa-salazar-a7a3701|80 ; https://cr.linkedin.com/in/vanessa-salazar-rosales-01890040|80 ; https://cr.linkedin.com/in/vanessa-salazar-25777410a|80</t>
         </is>
       </c>
       <c r="L728" t="inlineStr">
@@ -49253,7 +49253,7 @@
       </c>
       <c r="K729" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/vanessa-salazar-a7a3701|80 ; https://cr.linkedin.com/in/vanessa-salazar-25777410a|80 ; https://cr.linkedin.com/in/vanessa-salazar-rosales-01890040|80</t>
+          <t>https://www.linkedin.com/in/vanessa-salazar-a7a3701|80 ; https://cr.linkedin.com/in/vanessa-salazar-rosales-01890040|80 ; https://cr.linkedin.com/in/vanessa-salazar-25777410a|80</t>
         </is>
       </c>
       <c r="L729" t="inlineStr">
@@ -49327,7 +49327,7 @@
       </c>
       <c r="K730" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/vanessa-salazar-a7a3701|80 ; https://cr.linkedin.com/in/vanessa-salazar-25777410a|80 ; https://cr.linkedin.com/in/vanessa-salazar-rosales-01890040|80</t>
+          <t>https://www.linkedin.com/in/vanessa-salazar-a7a3701|80 ; https://cr.linkedin.com/in/vanessa-salazar-rosales-01890040|80 ; https://cr.linkedin.com/in/vanessa-salazar-25777410a|80</t>
         </is>
       </c>
       <c r="L730" t="inlineStr">
@@ -52873,11 +52873,11 @@
       </c>
       <c r="G784" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://eg.linkedin.com/in/angie-viquez-b3441a48</t>
         </is>
       </c>
       <c r="H784" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I784" t="inlineStr">
         <is>
@@ -52891,7 +52891,7 @@
       </c>
       <c r="K784" t="inlineStr">
         <is>
-          <t>https://cr.linkedin.com/in/angie-rojas-0b9389302|75 ; https://cr.linkedin.com/in/angie-rojas-obando-0053a8228|75 ; https://cr.linkedin.com/in/angie-rojas-252559113|75</t>
+          <t>https://eg.linkedin.com/in/angie-viquez-b3441a48|80 ; https://cr.linkedin.com/in/angie-rojas-0b9389302|75 ; https://cr.linkedin.com/in/angie-rojas-obando-0053a8228|75</t>
         </is>
       </c>
       <c r="L784" t="inlineStr">
@@ -53615,7 +53615,7 @@
       </c>
       <c r="K794" t="inlineStr">
         <is>
-          <t>https://cr.linkedin.com/in/alejandro-rodriguez-sanabria-730a68340|100 ; https://cr.linkedin.com/in/alejandro-rodr%C3%ADguez-ab5188387|100</t>
+          <t>https://cr.linkedin.com/in/alejandro-rodriguez-sanabria-730a68340|100</t>
         </is>
       </c>
       <c r="L794" t="inlineStr">
@@ -53879,7 +53879,7 @@
       </c>
       <c r="K798" t="inlineStr">
         <is>
-          <t>https://cr.linkedin.com/in/francisca-mar%C3%ADa-hern%C3%A1ndez-mu%C3%B1oz-811299129|100 ; https://www.linkedin.com/in/maria-guadalupe-hernandez|83 ; https://www.linkedin.com/in/maria-hernandez-a256781a1|80</t>
+          <t>https://cr.linkedin.com/in/francisca-mar%C3%ADa-hern%C3%A1ndez-mu%C3%B1oz-811299129|100 ; https://www.linkedin.com/in/maria-guadalupe-hernandez|83 ; https://pa.linkedin.com/in/mar%C3%ADa-hernandez-736391252|80</t>
         </is>
       </c>
       <c r="L798" t="inlineStr">
@@ -54685,7 +54685,7 @@
       </c>
       <c r="G810" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/diego-espinoza-135909111</t>
         </is>
       </c>
       <c r="H810" t="n">
@@ -54703,7 +54703,7 @@
       </c>
       <c r="K810" t="inlineStr">
         <is>
-          <t>https://cr.linkedin.com/in/diego-espinoza-herrera-7807a095|100 ; https://cr.linkedin.com/in/diego-espinoza-135909111|100</t>
+          <t>https://cr.linkedin.com/in/diego-espinoza-135909111|100</t>
         </is>
       </c>
       <c r="L810" t="inlineStr">
@@ -54999,7 +54999,7 @@
       </c>
       <c r="K814" t="inlineStr">
         <is>
-          <t>https://co.linkedin.com/in/sofia-marin-henao-8751a32b6|80 ; https://cr.linkedin.com/in/sofia-angulo-cordero-937251162|75</t>
+          <t>https://co.linkedin.com/in/sofia-marin-henao-8751a32b6|80 ; https://co.linkedin.com/in/sofia-marin-n%C3%BA%C3%B1ez-2a9008258|80 ; https://cr.linkedin.com/in/sofia-angulo-cordero-937251162|75</t>
         </is>
       </c>
       <c r="L814" t="inlineStr">
@@ -55393,11 +55393,11 @@
       </c>
       <c r="G820" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://mx.linkedin.com/in/oscar-ruiz-acosta-805291124/en</t>
         </is>
       </c>
       <c r="H820" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I820" t="inlineStr">
         <is>
@@ -55406,12 +55406,12 @@
       </c>
       <c r="J820" t="inlineStr">
         <is>
-          <t>ESTUDIA</t>
+          <t>NO DETERMINADO</t>
         </is>
       </c>
       <c r="K820" t="inlineStr">
         <is>
-          <t>https://cr.linkedin.com/in/%C3%B3scar-castro-ruiz-7a9230179|80 ; https://cr.linkedin.com/in/steven-ruiz-2a28abb7|80</t>
+          <t>https://mx.linkedin.com/in/oscar-ruiz-acosta-805291124/en|90 ; https://cr.linkedin.com/in/%C3%B3scar-castro-ruiz-7a9230179|80 ; https://cr.linkedin.com/in/steven-ruiz-2a28abb7|80</t>
         </is>
       </c>
       <c r="L820" t="inlineStr">
@@ -55426,7 +55426,7 @@
       </c>
       <c r="N820" t="inlineStr">
         <is>
-          <t>SIN INFO</t>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="O820" t="inlineStr">
@@ -57235,15 +57235,15 @@
       </c>
       <c r="G849" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://pa.linkedin.com/in/rodrigo-el%C3%ADas-rodriguez-0b8523193</t>
         </is>
       </c>
       <c r="H849" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I849" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J849" t="inlineStr">
@@ -57251,10 +57251,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K849" t="inlineStr"/>
-      <c r="L849" t="inlineStr"/>
-      <c r="M849" t="inlineStr"/>
-      <c r="N849" t="inlineStr"/>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>https://pa.linkedin.com/in/rodrigo-el%C3%ADas-rodriguez-0b8523193|90 ; https://pa.linkedin.com/in/diego-rodriguez-gonzalez-a61b842a8|83 ; https://cr.linkedin.com/in/diego-rodriguez-b70862121|80</t>
+        </is>
+      </c>
+      <c r="L849" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M849" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N849" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
       <c r="O849" t="inlineStr">
         <is>
           <t>503480689</t>
@@ -57293,15 +57309,15 @@
       </c>
       <c r="G850" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/deylin-rueda-p%C3%A9rez-47199a243</t>
         </is>
       </c>
       <c r="H850" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I850" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J850" t="inlineStr">
@@ -57309,10 +57325,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K850" t="inlineStr"/>
-      <c r="L850" t="inlineStr"/>
-      <c r="M850" t="inlineStr"/>
-      <c r="N850" t="inlineStr"/>
+      <c r="K850" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/deylin-rueda-p%C3%A9rez-47199a243|100</t>
+        </is>
+      </c>
+      <c r="L850" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M850" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N850" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O850" t="inlineStr">
         <is>
           <t>503480716</t>
@@ -57351,15 +57383,15 @@
       </c>
       <c r="G851" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/mariana-navarro-monge-398819101</t>
         </is>
       </c>
       <c r="H851" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I851" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J851" t="inlineStr">
@@ -57367,10 +57399,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K851" t="inlineStr"/>
-      <c r="L851" t="inlineStr"/>
-      <c r="M851" t="inlineStr"/>
-      <c r="N851" t="inlineStr"/>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/mariana-navarro-monge-398819101|100</t>
+        </is>
+      </c>
+      <c r="L851" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M851" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N851" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O851" t="inlineStr">
         <is>
           <t>503480861</t>
@@ -57413,11 +57461,11 @@
         </is>
       </c>
       <c r="H852" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I852" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J852" t="inlineStr">
@@ -57425,10 +57473,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K852" t="inlineStr"/>
-      <c r="L852" t="inlineStr"/>
-      <c r="M852" t="inlineStr"/>
-      <c r="N852" t="inlineStr"/>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/mariana-navarro-monge-398819101|100</t>
+        </is>
+      </c>
+      <c r="L852" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M852" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N852" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O852" t="inlineStr">
         <is>
           <t>503480861</t>
@@ -57583,15 +57647,15 @@
       </c>
       <c r="G855" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://ar.linkedin.com/in/walter-morales-b3186b57</t>
         </is>
       </c>
       <c r="H855" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J855" t="inlineStr">
@@ -57599,10 +57663,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K855" t="inlineStr"/>
-      <c r="L855" t="inlineStr"/>
-      <c r="M855" t="inlineStr"/>
-      <c r="N855" t="inlineStr"/>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>https://ar.linkedin.com/in/walter-morales-b3186b57|80 ; https://gt.linkedin.com/in/walter-morales-ab4373260|80 ; https://cr.linkedin.com/in/walter-campos-014b6b5b|75</t>
+        </is>
+      </c>
+      <c r="L855" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M855" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N855" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O855" t="inlineStr">
         <is>
           <t>503490320</t>
@@ -57645,11 +57725,11 @@
         </is>
       </c>
       <c r="H856" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I856" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J856" t="inlineStr">
@@ -57657,10 +57737,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K856" t="inlineStr"/>
-      <c r="L856" t="inlineStr"/>
-      <c r="M856" t="inlineStr"/>
-      <c r="N856" t="inlineStr"/>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>https://ar.linkedin.com/in/walter-morales-b3186b57|80 ; https://gt.linkedin.com/in/walter-morales-ab4373260|80 ; https://cr.linkedin.com/in/walter-campos-014b6b5b|75</t>
+        </is>
+      </c>
+      <c r="L856" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M856" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N856" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O856" t="inlineStr">
         <is>
           <t>503490320</t>
@@ -57873,15 +57969,15 @@
       </c>
       <c r="G860" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/paul-steven-brice%C3%B1o-quintero-a5219140</t>
         </is>
       </c>
       <c r="H860" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I860" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J860" t="inlineStr">
@@ -57889,10 +57985,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K860" t="inlineStr"/>
-      <c r="L860" t="inlineStr"/>
-      <c r="M860" t="inlineStr"/>
-      <c r="N860" t="inlineStr"/>
+      <c r="K860" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/paul-steven-brice%C3%B1o-quintero-a5219140|100</t>
+        </is>
+      </c>
+      <c r="L860" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M860" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N860" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O860" t="inlineStr">
         <is>
           <t>503490580</t>
@@ -57935,11 +58047,11 @@
         </is>
       </c>
       <c r="H861" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I861" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J861" t="inlineStr">
@@ -57947,10 +58059,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K861" t="inlineStr"/>
-      <c r="L861" t="inlineStr"/>
-      <c r="M861" t="inlineStr"/>
-      <c r="N861" t="inlineStr"/>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/paul-steven-brice%C3%B1o-quintero-a5219140|100</t>
+        </is>
+      </c>
+      <c r="L861" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M861" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N861" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O861" t="inlineStr">
         <is>
           <t>503490580</t>
@@ -57989,15 +58117,15 @@
       </c>
       <c r="G862" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/kendall-angulo-022690a7</t>
         </is>
       </c>
       <c r="H862" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I862" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J862" t="inlineStr">
@@ -58005,10 +58133,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K862" t="inlineStr"/>
-      <c r="L862" t="inlineStr"/>
-      <c r="M862" t="inlineStr"/>
-      <c r="N862" t="inlineStr"/>
+      <c r="K862" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/kendall-angulo-022690a7|80</t>
+        </is>
+      </c>
+      <c r="L862" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M862" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N862" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O862" t="inlineStr">
         <is>
           <t>503490753</t>
@@ -58047,15 +58191,15 @@
       </c>
       <c r="G863" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/hellen-camacho-miranda-65732a191</t>
         </is>
       </c>
       <c r="H863" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I863" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J863" t="inlineStr">
@@ -58063,10 +58207,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K863" t="inlineStr"/>
-      <c r="L863" t="inlineStr"/>
-      <c r="M863" t="inlineStr"/>
-      <c r="N863" t="inlineStr"/>
+      <c r="K863" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/hellen-camacho-miranda-65732a191|80</t>
+        </is>
+      </c>
+      <c r="L863" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M863" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N863" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O863" t="inlineStr">
         <is>
           <t>503490760</t>
@@ -58105,15 +58265,15 @@
       </c>
       <c r="G864" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://pe.linkedin.com/in/veronica-castillo-b38b3831</t>
         </is>
       </c>
       <c r="H864" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I864" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J864" t="inlineStr">
@@ -58121,10 +58281,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K864" t="inlineStr"/>
-      <c r="L864" t="inlineStr"/>
-      <c r="M864" t="inlineStr"/>
-      <c r="N864" t="inlineStr"/>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>https://pe.linkedin.com/in/veronica-castillo-b38b3831|80 ; https://ec.linkedin.com/in/ver%C3%B3nica-castillo-917b6b21b|80 ; https://cr.linkedin.com/in/veronica-rodriguez-lara-a84a8766|75</t>
+        </is>
+      </c>
+      <c r="L864" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M864" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N864" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O864" t="inlineStr">
         <is>
           <t>503490840</t>
@@ -58167,11 +58343,11 @@
         </is>
       </c>
       <c r="H865" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I865" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J865" t="inlineStr">
@@ -58179,10 +58355,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K865" t="inlineStr"/>
-      <c r="L865" t="inlineStr"/>
-      <c r="M865" t="inlineStr"/>
-      <c r="N865" t="inlineStr"/>
+      <c r="K865" t="inlineStr">
+        <is>
+          <t>https://pe.linkedin.com/in/veronica-castillo-b38b3831|80 ; https://ec.linkedin.com/in/ver%C3%B3nica-castillo-917b6b21b|80 ; https://cr.linkedin.com/in/veronica-rodriguez-lara-a84a8766|75</t>
+        </is>
+      </c>
+      <c r="L865" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M865" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N865" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O865" t="inlineStr">
         <is>
           <t>503490840</t>
@@ -58225,11 +58417,11 @@
         </is>
       </c>
       <c r="H866" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="I866" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J866" t="inlineStr">
@@ -58237,10 +58429,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K866" t="inlineStr"/>
-      <c r="L866" t="inlineStr"/>
-      <c r="M866" t="inlineStr"/>
-      <c r="N866" t="inlineStr"/>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>https://pe.linkedin.com/in/veronica-castillo-b38b3831|83 ; https://ec.linkedin.com/in/ver%C3%B3nica-castillo-917b6b21b|83 ; https://pa.linkedin.com/in/veronica-rodriguez-84735522a/es|78</t>
+        </is>
+      </c>
+      <c r="L866" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M866" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N866" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O866" t="inlineStr">
         <is>
           <t>503490840</t>
@@ -58279,15 +58487,15 @@
       </c>
       <c r="G867" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/daniela-gutierrez-27073a235</t>
         </is>
       </c>
       <c r="H867" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I867" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J867" t="inlineStr">
@@ -58295,10 +58503,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K867" t="inlineStr"/>
-      <c r="L867" t="inlineStr"/>
-      <c r="M867" t="inlineStr"/>
-      <c r="N867" t="inlineStr"/>
+      <c r="K867" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/daniela-gutierrez-27073a235|80 ; https://cr.linkedin.com/in/daniela-guti%C3%A9rrez-chavarr%C3%ADa-140ba2296|80 ; https://cr.linkedin.com/in/daniela-guti%C3%A9rrez-6ab98415|80</t>
+        </is>
+      </c>
+      <c r="L867" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M867" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N867" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O867" t="inlineStr">
         <is>
           <t>503490875</t>
@@ -58337,15 +58561,15 @@
       </c>
       <c r="G868" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/gabriela-alvarez-9778a475</t>
         </is>
       </c>
       <c r="H868" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I868" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J868" t="inlineStr">
@@ -58353,10 +58577,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K868" t="inlineStr"/>
-      <c r="L868" t="inlineStr"/>
-      <c r="M868" t="inlineStr"/>
-      <c r="N868" t="inlineStr"/>
+      <c r="K868" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/gabriela-alvarez-9778a475|100 ; https://pa.linkedin.com/in/alejandra-alvarez-25344122a|83 ; https://cr.linkedin.com/in/alejandra-alvarez-b7076b152|80</t>
+        </is>
+      </c>
+      <c r="L868" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M868" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N868" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O868" t="inlineStr">
         <is>
           <t>503490927</t>
@@ -58395,15 +58635,15 @@
       </c>
       <c r="G869" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/roberto-cerdas-jim%C3%A9nez-4aa08538</t>
         </is>
       </c>
       <c r="H869" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I869" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J869" t="inlineStr">
@@ -58411,10 +58651,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K869" t="inlineStr"/>
-      <c r="L869" t="inlineStr"/>
-      <c r="M869" t="inlineStr"/>
-      <c r="N869" t="inlineStr"/>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/jose-cerdas-arguedas-4ba57225|90 ; https://cr.linkedin.com/in/roberto-cerdas-jim%C3%A9nez-4aa08538|80</t>
+        </is>
+      </c>
+      <c r="L869" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M869" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N869" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O869" t="inlineStr">
         <is>
           <t>503500054</t>
@@ -58453,15 +58709,15 @@
       </c>
       <c r="G870" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/ana-elena-chavarria-a7110a56</t>
         </is>
       </c>
       <c r="H870" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I870" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J870" t="inlineStr">
@@ -58469,10 +58725,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K870" t="inlineStr"/>
-      <c r="L870" t="inlineStr"/>
-      <c r="M870" t="inlineStr"/>
-      <c r="N870" t="inlineStr"/>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/ana-elena-chavarria-a7110a56|80</t>
+        </is>
+      </c>
+      <c r="L870" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M870" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N870" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O870" t="inlineStr">
         <is>
           <t>503500120</t>
@@ -58515,11 +58787,11 @@
         </is>
       </c>
       <c r="H871" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I871" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J871" t="inlineStr">
@@ -58527,10 +58799,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K871" t="inlineStr"/>
-      <c r="L871" t="inlineStr"/>
-      <c r="M871" t="inlineStr"/>
-      <c r="N871" t="inlineStr"/>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/ana-elena-chavarria-a7110a56|80</t>
+        </is>
+      </c>
+      <c r="L871" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M871" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N871" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O871" t="inlineStr">
         <is>
           <t>503500120</t>
@@ -58569,15 +58857,15 @@
       </c>
       <c r="G872" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/raquel-p%C3%A9rez-solano-795946126</t>
         </is>
       </c>
       <c r="H872" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="I872" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J872" t="inlineStr">
@@ -58585,10 +58873,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K872" t="inlineStr"/>
-      <c r="L872" t="inlineStr"/>
-      <c r="M872" t="inlineStr"/>
-      <c r="N872" t="inlineStr"/>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/raquel-p%C3%A9rez-solano-795946126|83 ; https://mx.linkedin.com/in/raquel-perez-a9aa0225|80 ; https://pa.linkedin.com/in/raquel-perez-35127411a|80</t>
+        </is>
+      </c>
+      <c r="L872" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M872" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N872" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O872" t="inlineStr">
         <is>
           <t>503500180</t>
@@ -58627,15 +58931,15 @@
       </c>
       <c r="G873" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/abraham-%C3%A1lvarez-alfaro-16b586229/en?trk=people-guest_people_search-card</t>
         </is>
       </c>
       <c r="H873" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I873" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J873" t="inlineStr">
@@ -58643,10 +58947,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K873" t="inlineStr"/>
-      <c r="L873" t="inlineStr"/>
-      <c r="M873" t="inlineStr"/>
-      <c r="N873" t="inlineStr"/>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/abraham-%C3%A1lvarez-alfaro-16b586229/en?trk=people-guest_people_search-card|80 ; https://pa.linkedin.com/in/jos%C3%A9-%C3%A1lvarez-622307308|80 ; https://cr.linkedin.com/in/jos%C3%A9-alvarez-9aaa8b45|80</t>
+        </is>
+      </c>
+      <c r="L873" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M873" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N873" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O873" t="inlineStr">
         <is>
           <t>503500232</t>
@@ -58801,15 +59121,15 @@
       </c>
       <c r="G876" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/rodolfo-araya-b2b81b1a3</t>
         </is>
       </c>
       <c r="H876" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I876" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J876" t="inlineStr">
@@ -58817,10 +59137,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K876" t="inlineStr"/>
-      <c r="L876" t="inlineStr"/>
-      <c r="M876" t="inlineStr"/>
-      <c r="N876" t="inlineStr"/>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/rodolfo-araya-b2b81b1a3|80</t>
+        </is>
+      </c>
+      <c r="L876" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M876" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N876" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O876" t="inlineStr">
         <is>
           <t>503500507</t>
@@ -58859,15 +59195,15 @@
       </c>
       <c r="G877" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://pa.linkedin.com/in/vanessa-herrera-263181282</t>
         </is>
       </c>
       <c r="H877" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="I877" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J877" t="inlineStr">
@@ -58875,10 +59211,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K877" t="inlineStr"/>
-      <c r="L877" t="inlineStr"/>
-      <c r="M877" t="inlineStr"/>
-      <c r="N877" t="inlineStr"/>
+      <c r="K877" t="inlineStr">
+        <is>
+          <t>https://pa.linkedin.com/in/vanessa-herrera-263181282|86 ; https://pa.linkedin.com/in/vanessa-herrera-50b12222a|80</t>
+        </is>
+      </c>
+      <c r="L877" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M877" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N877" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O877" t="inlineStr">
         <is>
           <t>503500549</t>
@@ -58917,26 +59269,42 @@
       </c>
       <c r="G878" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/maria-g%C3%B3mez-zamora-6b4036306</t>
         </is>
       </c>
       <c r="H878" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I878" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J878" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K878" t="inlineStr"/>
-      <c r="L878" t="inlineStr"/>
-      <c r="M878" t="inlineStr"/>
-      <c r="N878" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K878" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/maria-g%C3%B3mez-zamora-6b4036306|80 ; https://mx.linkedin.com/in/mar%C3%ADa-zamora-0a1b6176|80</t>
+        </is>
+      </c>
+      <c r="L878" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M878" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N878" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O878" t="inlineStr">
         <is>
           <t>503500630</t>
@@ -58975,15 +59343,15 @@
       </c>
       <c r="G879" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/miriam-mondrag%C3%B3n-guill%C3%A9n-1ba23354</t>
         </is>
       </c>
       <c r="H879" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I879" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J879" t="inlineStr">
@@ -58991,10 +59359,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K879" t="inlineStr"/>
-      <c r="L879" t="inlineStr"/>
-      <c r="M879" t="inlineStr"/>
-      <c r="N879" t="inlineStr"/>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/miriam-mondrag%C3%B3n-guill%C3%A9n-1ba23354|100</t>
+        </is>
+      </c>
+      <c r="L879" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M879" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N879" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O879" t="inlineStr">
         <is>
           <t>503500650</t>
@@ -59033,15 +59417,15 @@
       </c>
       <c r="G880" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/diego-angulo-98aabb188</t>
         </is>
       </c>
       <c r="H880" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I880" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J880" t="inlineStr">
@@ -59049,10 +59433,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K880" t="inlineStr"/>
-      <c r="L880" t="inlineStr"/>
-      <c r="M880" t="inlineStr"/>
-      <c r="N880" t="inlineStr"/>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/diego-angulo-98aabb188|80 ; https://cr.linkedin.com/in/diego-angulo-rodr%C3%ADguez-686368163|80 ; https://cr.linkedin.com/in/diego-angulo-85a28415a|80</t>
+        </is>
+      </c>
+      <c r="L880" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M880" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N880" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O880" t="inlineStr">
         <is>
           <t>503500679</t>
@@ -59211,11 +59611,11 @@
         </is>
       </c>
       <c r="H883" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I883" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="J883" t="inlineStr">
@@ -59223,10 +59623,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K883" t="inlineStr"/>
-      <c r="L883" t="inlineStr"/>
-      <c r="M883" t="inlineStr"/>
-      <c r="N883" t="inlineStr"/>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/efrain-rodriguez-b023a422|60</t>
+        </is>
+      </c>
+      <c r="L883" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M883" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N883" t="inlineStr">
+        <is>
+          <t>NO COINCIDE</t>
+        </is>
+      </c>
       <c r="O883" t="inlineStr">
         <is>
           <t>503510078</t>
@@ -59265,15 +59681,15 @@
       </c>
       <c r="G884" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/melissa-rosales-alfaro</t>
         </is>
       </c>
       <c r="H884" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I884" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J884" t="inlineStr">
@@ -59281,10 +59697,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K884" t="inlineStr"/>
-      <c r="L884" t="inlineStr"/>
-      <c r="M884" t="inlineStr"/>
-      <c r="N884" t="inlineStr"/>
+      <c r="K884" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/melissa-rosales-alfaro|100</t>
+        </is>
+      </c>
+      <c r="L884" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M884" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N884" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O884" t="inlineStr">
         <is>
           <t>503510189</t>
@@ -59323,15 +59755,15 @@
       </c>
       <c r="G885" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/luis-umana-palavicini-671089249</t>
         </is>
       </c>
       <c r="H885" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I885" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J885" t="inlineStr">
@@ -59339,10 +59771,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K885" t="inlineStr"/>
-      <c r="L885" t="inlineStr"/>
-      <c r="M885" t="inlineStr"/>
-      <c r="N885" t="inlineStr"/>
+      <c r="K885" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/luis-umana-palavicini-671089249|80</t>
+        </is>
+      </c>
+      <c r="L885" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M885" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N885" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O885" t="inlineStr">
         <is>
           <t>503510197</t>
@@ -59381,15 +59829,15 @@
       </c>
       <c r="G886" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://mx.linkedin.com/in/maria-delgado-14141622</t>
         </is>
       </c>
       <c r="H886" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I886" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J886" t="inlineStr">
@@ -59397,10 +59845,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K886" t="inlineStr"/>
-      <c r="L886" t="inlineStr"/>
-      <c r="M886" t="inlineStr"/>
-      <c r="N886" t="inlineStr"/>
+      <c r="K886" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/in/maria-delgado-14141622|80 ; https://www.linkedin.com/in/maria-delgado-57a369bb|80 ; https://pa.linkedin.com/in/maria-caridad-delgado-30308954|80</t>
+        </is>
+      </c>
+      <c r="L886" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M886" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N886" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O886" t="inlineStr">
         <is>
           <t>503510444</t>
@@ -59439,15 +59903,15 @@
       </c>
       <c r="G887" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/adriana-g%C3%B3mez-71abbb208</t>
         </is>
       </c>
       <c r="H887" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I887" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J887" t="inlineStr">
@@ -59455,10 +59919,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K887" t="inlineStr"/>
-      <c r="L887" t="inlineStr"/>
-      <c r="M887" t="inlineStr"/>
-      <c r="N887" t="inlineStr"/>
+      <c r="K887" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/adriana-g%C3%B3mez-71abbb208|80 ; https://cr.linkedin.com/in/adriana-g%C3%B3mez-jim%C3%A9nez-23090530b|80</t>
+        </is>
+      </c>
+      <c r="L887" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M887" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N887" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O887" t="inlineStr">
         <is>
           <t>503510461</t>
@@ -59501,11 +59981,11 @@
         </is>
       </c>
       <c r="H888" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I888" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J888" t="inlineStr">
@@ -59513,10 +59993,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K888" t="inlineStr"/>
-      <c r="L888" t="inlineStr"/>
-      <c r="M888" t="inlineStr"/>
-      <c r="N888" t="inlineStr"/>
+      <c r="K888" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/adriana-g%C3%B3mez-71abbb208|80 ; https://cr.linkedin.com/in/adriana-g%C3%B3mez-jim%C3%A9nez-23090530b|80</t>
+        </is>
+      </c>
+      <c r="L888" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M888" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N888" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O888" t="inlineStr">
         <is>
           <t>503510461</t>
@@ -59613,15 +60109,15 @@
       </c>
       <c r="G890" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/juan-carlos-fernandez-9575a634</t>
         </is>
       </c>
       <c r="H890" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I890" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J890" t="inlineStr">
@@ -59629,10 +60125,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K890" t="inlineStr"/>
-      <c r="L890" t="inlineStr"/>
-      <c r="M890" t="inlineStr"/>
-      <c r="N890" t="inlineStr"/>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/juan-carlos-fernandez-9575a634|90 ; https://cr.linkedin.com/in/carlos-fernandez-020a5318a|80 ; https://cr.linkedin.com/in/carlos-fernandez-navarro-698912126|80</t>
+        </is>
+      </c>
+      <c r="L890" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M890" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N890" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O890" t="inlineStr">
         <is>
           <t>503510624</t>
@@ -59675,11 +60187,11 @@
         </is>
       </c>
       <c r="H891" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I891" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J891" t="inlineStr">
@@ -59687,10 +60199,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K891" t="inlineStr"/>
-      <c r="L891" t="inlineStr"/>
-      <c r="M891" t="inlineStr"/>
-      <c r="N891" t="inlineStr"/>
+      <c r="K891" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/juan-carlos-fernandez-9575a634|90 ; https://cr.linkedin.com/in/carlos-fernandez-020a5318a|80 ; https://cr.linkedin.com/in/carlos-fernandez-navarro-698912126|80</t>
+        </is>
+      </c>
+      <c r="L891" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M891" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N891" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O891" t="inlineStr">
         <is>
           <t>503510624</t>
@@ -59787,26 +60315,42 @@
       </c>
       <c r="G893" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/maria-ramirez-a998a313a</t>
         </is>
       </c>
       <c r="H893" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I893" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J893" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K893" t="inlineStr"/>
-      <c r="L893" t="inlineStr"/>
-      <c r="M893" t="inlineStr"/>
-      <c r="N893" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/maria-ramirez-a998a313a|80 ; https://pa.linkedin.com/in/mar%C3%ADa-ramir%C3%A9z-0969222a2?trk=people-guest_people_search-card|80 ; https://cr.linkedin.com/in/mar%C3%ADa-ramirez-5b9238151|80</t>
+        </is>
+      </c>
+      <c r="L893" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M893" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N893" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O893" t="inlineStr">
         <is>
           <t>503510626</t>
@@ -59961,15 +60505,15 @@
       </c>
       <c r="G896" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/rebeca-lopez-sanchez-66299552</t>
         </is>
       </c>
       <c r="H896" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I896" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J896" t="inlineStr">
@@ -59977,10 +60521,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K896" t="inlineStr"/>
-      <c r="L896" t="inlineStr"/>
-      <c r="M896" t="inlineStr"/>
-      <c r="N896" t="inlineStr"/>
+      <c r="K896" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/rebeca-lopez-sanchez-66299552|100 ; https://cr.linkedin.com/in/rebeca-lopez-sequeira-913624120|80 ; https://cr.linkedin.com/in/mar%C3%ADa-l%C3%B3pez-1b5534192|80</t>
+        </is>
+      </c>
+      <c r="L896" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M896" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N896" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O896" t="inlineStr">
         <is>
           <t>503520099</t>
@@ -60023,11 +60583,11 @@
         </is>
       </c>
       <c r="H897" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I897" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J897" t="inlineStr">
@@ -60035,10 +60595,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K897" t="inlineStr"/>
-      <c r="L897" t="inlineStr"/>
-      <c r="M897" t="inlineStr"/>
-      <c r="N897" t="inlineStr"/>
+      <c r="K897" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/rebeca-lopez-sanchez-66299552|100 ; https://cr.linkedin.com/in/rebeca-lopez-sequeira-913624120|80 ; https://cr.linkedin.com/in/mar%C3%ADa-l%C3%B3pez-1b5534192|80</t>
+        </is>
+      </c>
+      <c r="L897" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M897" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N897" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O897" t="inlineStr">
         <is>
           <t>503520099</t>
@@ -60077,15 +60653,15 @@
       </c>
       <c r="G898" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://sv.linkedin.com/in/francisco-lopez-rom%C3%A1n-91244721</t>
         </is>
       </c>
       <c r="H898" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="I898" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J898" t="inlineStr">
@@ -60093,10 +60669,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K898" t="inlineStr"/>
-      <c r="L898" t="inlineStr"/>
-      <c r="M898" t="inlineStr"/>
-      <c r="N898" t="inlineStr"/>
+      <c r="K898" t="inlineStr">
+        <is>
+          <t>https://pa.linkedin.com/in/abner-lopez-185608207|86 ; https://sv.linkedin.com/in/francisco-lopez-rom%C3%A1n-91244721|83 ; https://cr.linkedin.com/in/francisco-l%C3%B3pez-fuentes-74829a42|83</t>
+        </is>
+      </c>
+      <c r="L898" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M898" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N898" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O898" t="inlineStr">
         <is>
           <t>503520105</t>
@@ -60135,15 +60727,15 @@
       </c>
       <c r="G899" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/vanessa-lopez-rudnik-9669686a</t>
         </is>
       </c>
       <c r="H899" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I899" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J899" t="inlineStr">
@@ -60151,10 +60743,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K899" t="inlineStr"/>
-      <c r="L899" t="inlineStr"/>
-      <c r="M899" t="inlineStr"/>
-      <c r="N899" t="inlineStr"/>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/vanessa-lopez-rudnik-9669686a|80 ; https://www.linkedin.com/in/vanessa-lopez-mejia-3a17536a|80</t>
+        </is>
+      </c>
+      <c r="L899" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M899" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N899" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O899" t="inlineStr">
         <is>
           <t>503520271</t>
@@ -60197,11 +60805,11 @@
         </is>
       </c>
       <c r="H900" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I900" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J900" t="inlineStr">
@@ -60209,10 +60817,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K900" t="inlineStr"/>
-      <c r="L900" t="inlineStr"/>
-      <c r="M900" t="inlineStr"/>
-      <c r="N900" t="inlineStr"/>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/vanessa-lopez-rudnik-9669686a|80 ; https://www.linkedin.com/in/vanessa-lopez-mejia-3a17536a|80</t>
+        </is>
+      </c>
+      <c r="L900" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M900" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N900" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O900" t="inlineStr">
         <is>
           <t>503520271</t>
@@ -60251,15 +60875,15 @@
       </c>
       <c r="G901" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/tatiana-obando-matamoros-34978b12a</t>
         </is>
       </c>
       <c r="H901" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I901" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J901" t="inlineStr">
@@ -60267,10 +60891,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K901" t="inlineStr"/>
-      <c r="L901" t="inlineStr"/>
-      <c r="M901" t="inlineStr"/>
-      <c r="N901" t="inlineStr"/>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/tatiana-obando-matamoros-34978b12a|80</t>
+        </is>
+      </c>
+      <c r="L901" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M901" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N901" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O901" t="inlineStr">
         <is>
           <t>503520342</t>
@@ -60425,15 +61065,15 @@
       </c>
       <c r="G904" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/yenifer-jaen-7686bb97</t>
         </is>
       </c>
       <c r="H904" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I904" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J904" t="inlineStr">
@@ -60441,10 +61081,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K904" t="inlineStr"/>
-      <c r="L904" t="inlineStr"/>
-      <c r="M904" t="inlineStr"/>
-      <c r="N904" t="inlineStr"/>
+      <c r="K904" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/yenifer-jaen-7686bb97|75</t>
+        </is>
+      </c>
+      <c r="L904" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M904" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N904" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O904" t="inlineStr">
         <is>
           <t>503520529</t>
@@ -60889,15 +61545,15 @@
       </c>
       <c r="G912" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/cristina-z%C3%BA%C3%B1iga-ram%C3%ADrez-803369113/es</t>
         </is>
       </c>
       <c r="H912" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I912" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J912" t="inlineStr">
@@ -60905,10 +61561,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K912" t="inlineStr"/>
-      <c r="L912" t="inlineStr"/>
-      <c r="M912" t="inlineStr"/>
-      <c r="N912" t="inlineStr"/>
+      <c r="K912" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/cristina-z%C3%BA%C3%B1iga-ram%C3%ADrez-803369113/es|80 ; https://cl.linkedin.com/in/cristina-zu%C3%B1iga-paredes|60</t>
+        </is>
+      </c>
+      <c r="L912" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M912" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N912" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O912" t="inlineStr">
         <is>
           <t>503520924</t>
@@ -61063,15 +61735,15 @@
       </c>
       <c r="G915" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/karol-jimenez-82002527</t>
         </is>
       </c>
       <c r="H915" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I915" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J915" t="inlineStr">
@@ -61079,10 +61751,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K915" t="inlineStr"/>
-      <c r="L915" t="inlineStr"/>
-      <c r="M915" t="inlineStr"/>
-      <c r="N915" t="inlineStr"/>
+      <c r="K915" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/karol-jimenez-82002527|75 ; https://cr.linkedin.com/in/karol-jimenez-04a74758|75 ; https://cr.linkedin.com/in/karol-jim%C3%A9nez-jara-531b07202/es|75</t>
+        </is>
+      </c>
+      <c r="L915" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M915" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N915" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O915" t="inlineStr">
         <is>
           <t>503530143</t>
@@ -61121,15 +61809,15 @@
       </c>
       <c r="G916" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://pa.linkedin.com/in/augusto-emilio-mendez-b573371a</t>
         </is>
       </c>
       <c r="H916" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I916" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J916" t="inlineStr">
@@ -61137,10 +61825,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K916" t="inlineStr"/>
-      <c r="L916" t="inlineStr"/>
-      <c r="M916" t="inlineStr"/>
-      <c r="N916" t="inlineStr"/>
+      <c r="K916" t="inlineStr">
+        <is>
+          <t>https://pa.linkedin.com/in/augusto-emilio-mendez-b573371a|80 ; https://cn.linkedin.com/in/emilio-mendez-5a9515b0|80</t>
+        </is>
+      </c>
+      <c r="L916" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M916" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N916" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O916" t="inlineStr">
         <is>
           <t>503530173</t>
@@ -61353,15 +62057,15 @@
       </c>
       <c r="G920" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/argery-obando-28880282</t>
         </is>
       </c>
       <c r="H920" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="I920" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J920" t="inlineStr">
@@ -61369,10 +62073,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K920" t="inlineStr"/>
-      <c r="L920" t="inlineStr"/>
-      <c r="M920" t="inlineStr"/>
-      <c r="N920" t="inlineStr"/>
+      <c r="K920" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/argery-obando-28880282|83</t>
+        </is>
+      </c>
+      <c r="L920" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M920" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N920" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O920" t="inlineStr">
         <is>
           <t>503530455</t>
@@ -61411,15 +62131,15 @@
       </c>
       <c r="G921" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://bo.linkedin.com/in/douglas-sanchez-pardo-5688a0145</t>
         </is>
       </c>
       <c r="H921" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I921" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J921" t="inlineStr">
@@ -61427,10 +62147,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K921" t="inlineStr"/>
-      <c r="L921" t="inlineStr"/>
-      <c r="M921" t="inlineStr"/>
-      <c r="N921" t="inlineStr"/>
+      <c r="K921" t="inlineStr">
+        <is>
+          <t>https://bo.linkedin.com/in/douglas-sanchez-pardo-5688a0145|90 ; https://cr.linkedin.com/in/douglas-s%C3%A1nchez-392b85151|80 ; https://cr.linkedin.com/in/douglas-sanchez-493b2311|80</t>
+        </is>
+      </c>
+      <c r="L921" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M921" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N921" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
       <c r="O921" t="inlineStr">
         <is>
           <t>503530620</t>
@@ -61469,15 +62205,15 @@
       </c>
       <c r="G922" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/tatiana-matarrita-8b077b37a</t>
         </is>
       </c>
       <c r="H922" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I922" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J922" t="inlineStr">
@@ -61485,10 +62221,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K922" t="inlineStr"/>
-      <c r="L922" t="inlineStr"/>
-      <c r="M922" t="inlineStr"/>
-      <c r="N922" t="inlineStr"/>
+      <c r="K922" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/tatiana-matarrita-8b077b37a|80</t>
+        </is>
+      </c>
+      <c r="L922" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M922" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N922" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O922" t="inlineStr">
         <is>
           <t>503530657</t>
@@ -61589,11 +62341,11 @@
         </is>
       </c>
       <c r="H924" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I924" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J924" t="inlineStr">
@@ -61601,10 +62353,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K924" t="inlineStr"/>
-      <c r="L924" t="inlineStr"/>
-      <c r="M924" t="inlineStr"/>
-      <c r="N924" t="inlineStr"/>
+      <c r="K924" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/in/maria-rosales-a359202a5|80 ; https://cr.linkedin.com/in/maria-rosales-aguilar-6a983523|80 ; https://ar.linkedin.com/in/alina-mar%C3%ADa-rosales-13b64141|80</t>
+        </is>
+      </c>
+      <c r="L924" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M924" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N924" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O924" t="inlineStr">
         <is>
           <t>503530824</t>
@@ -61759,15 +62527,15 @@
       </c>
       <c r="G927" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/gustavo-vargas-ramirez-73878267</t>
         </is>
       </c>
       <c r="H927" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I927" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J927" t="inlineStr">
@@ -61775,10 +62543,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K927" t="inlineStr"/>
-      <c r="L927" t="inlineStr"/>
-      <c r="M927" t="inlineStr"/>
-      <c r="N927" t="inlineStr"/>
+      <c r="K927" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/gustavo-vargas-ramirez-73878267|100 ; https://cr.linkedin.com/in/gustavo-vargas-42880a9a|80 ; https://cr.linkedin.com/in/gustavo-vargas-%C3%A1lvarez-67a170109|80</t>
+        </is>
+      </c>
+      <c r="L927" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M927" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N927" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O927" t="inlineStr">
         <is>
           <t>503530885</t>
@@ -61817,15 +62601,15 @@
       </c>
       <c r="G928" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/dinorah-ju%C3%A1rez-villarreal-8ba850117</t>
         </is>
       </c>
       <c r="H928" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="I928" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J928" t="inlineStr">
@@ -61833,10 +62617,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K928" t="inlineStr"/>
-      <c r="L928" t="inlineStr"/>
-      <c r="M928" t="inlineStr"/>
-      <c r="N928" t="inlineStr"/>
+      <c r="K928" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/dinorah-ju%C3%A1rez-villarreal-8ba850117|83 ; https://cr.linkedin.com/in/dinorah-juarez-213a4a1a7|83</t>
+        </is>
+      </c>
+      <c r="L928" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M928" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N928" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O928" t="inlineStr">
         <is>
           <t>503530939</t>
@@ -61879,11 +62679,11 @@
         </is>
       </c>
       <c r="H929" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="I929" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J929" t="inlineStr">
@@ -61891,10 +62691,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K929" t="inlineStr"/>
-      <c r="L929" t="inlineStr"/>
-      <c r="M929" t="inlineStr"/>
-      <c r="N929" t="inlineStr"/>
+      <c r="K929" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/dinorah-ju%C3%A1rez-villarreal-8ba850117|83 ; https://cr.linkedin.com/in/dinorah-juarez-213a4a1a7|83</t>
+        </is>
+      </c>
+      <c r="L929" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M929" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N929" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O929" t="inlineStr">
         <is>
           <t>503530939</t>
@@ -61933,15 +62749,15 @@
       </c>
       <c r="G930" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/wagner-castillo-espinoza-72064520b</t>
         </is>
       </c>
       <c r="H930" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I930" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J930" t="inlineStr">
@@ -61949,10 +62765,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K930" t="inlineStr"/>
-      <c r="L930" t="inlineStr"/>
-      <c r="M930" t="inlineStr"/>
-      <c r="N930" t="inlineStr"/>
+      <c r="K930" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/wagner-castillo-espinoza-72064520b|100 ; https://cr.linkedin.com/in/wagner-castillo-7a09553b|80</t>
+        </is>
+      </c>
+      <c r="L930" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M930" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N930" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O930" t="inlineStr">
         <is>
           <t>503530982</t>
@@ -61995,11 +62827,11 @@
         </is>
       </c>
       <c r="H931" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I931" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J931" t="inlineStr">
@@ -62007,10 +62839,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K931" t="inlineStr"/>
-      <c r="L931" t="inlineStr"/>
-      <c r="M931" t="inlineStr"/>
-      <c r="N931" t="inlineStr"/>
+      <c r="K931" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/wagner-castillo-espinoza-72064520b|100 ; https://cr.linkedin.com/in/wagner-castillo-7a09553b|80</t>
+        </is>
+      </c>
+      <c r="L931" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M931" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N931" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O931" t="inlineStr">
         <is>
           <t>503530982</t>
@@ -62049,15 +62897,15 @@
       </c>
       <c r="G932" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/ileana-quesada-387b50139</t>
         </is>
       </c>
       <c r="H932" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="I932" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J932" t="inlineStr">
@@ -62065,10 +62913,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K932" t="inlineStr"/>
-      <c r="L932" t="inlineStr"/>
-      <c r="M932" t="inlineStr"/>
-      <c r="N932" t="inlineStr"/>
+      <c r="K932" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/ileana-quesada-387b50139|83</t>
+        </is>
+      </c>
+      <c r="L932" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M932" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N932" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O932" t="inlineStr">
         <is>
           <t>503530983</t>
@@ -62111,11 +62975,11 @@
         </is>
       </c>
       <c r="H933" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="I933" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J933" t="inlineStr">
@@ -62123,10 +62987,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K933" t="inlineStr"/>
-      <c r="L933" t="inlineStr"/>
-      <c r="M933" t="inlineStr"/>
-      <c r="N933" t="inlineStr"/>
+      <c r="K933" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/ileana-quesada-387b50139|83</t>
+        </is>
+      </c>
+      <c r="L933" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M933" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N933" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O933" t="inlineStr">
         <is>
           <t>503530983</t>
@@ -62223,15 +63103,15 @@
       </c>
       <c r="G935" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://www.linkedin.com/in/ana-ruiz-123nc/es</t>
         </is>
       </c>
       <c r="H935" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I935" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J935" t="inlineStr">
@@ -62239,10 +63119,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K935" t="inlineStr"/>
-      <c r="L935" t="inlineStr"/>
-      <c r="M935" t="inlineStr"/>
-      <c r="N935" t="inlineStr"/>
+      <c r="K935" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ana-ruiz-123nc/es|80 ; https://es.linkedin.com/in/ana-ruiz-moya-94552015b|80</t>
+        </is>
+      </c>
+      <c r="L935" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M935" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N935" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O935" t="inlineStr">
         <is>
           <t>503540413</t>
@@ -62339,15 +63235,15 @@
       </c>
       <c r="G937" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://sv.linkedin.com/in/andr%C3%A9s-mart%C3%ADnez-201055106</t>
         </is>
       </c>
       <c r="H937" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="I937" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J937" t="inlineStr">
@@ -62355,10 +63251,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K937" t="inlineStr"/>
-      <c r="L937" t="inlineStr"/>
-      <c r="M937" t="inlineStr"/>
-      <c r="N937" t="inlineStr"/>
+      <c r="K937" t="inlineStr">
+        <is>
+          <t>https://sv.linkedin.com/in/andr%C3%A9s-mart%C3%ADnez-201055106|83 ; https://pa.linkedin.com/in/carlos-martinez-235069225|80 ; https://www.linkedin.com/in/carlos-martinez-100percent/es|80</t>
+        </is>
+      </c>
+      <c r="L937" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M937" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N937" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O937" t="inlineStr">
         <is>
           <t>503540493</t>
@@ -62401,22 +63313,38 @@
         </is>
       </c>
       <c r="H938" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I938" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J938" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K938" t="inlineStr"/>
-      <c r="L938" t="inlineStr"/>
-      <c r="M938" t="inlineStr"/>
-      <c r="N938" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K938" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/mar%C3%ADa-l%C3%B3pez-1b5534192|80 ; https://cr.linkedin.com/in/maria-lopez-a17630174|80 ; https://pa.linkedin.com/in/maria-lopez-074456115|80</t>
+        </is>
+      </c>
+      <c r="L938" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M938" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N938" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O938" t="inlineStr">
         <is>
           <t>503540544</t>
@@ -62513,26 +63441,42 @@
       </c>
       <c r="G940" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/dinnia-diaz-159a2a31</t>
         </is>
       </c>
       <c r="H940" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I940" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J940" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K940" t="inlineStr"/>
-      <c r="L940" t="inlineStr"/>
-      <c r="M940" t="inlineStr"/>
-      <c r="N940" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K940" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/dinnia-diaz-159a2a31|80</t>
+        </is>
+      </c>
+      <c r="L940" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M940" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N940" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O940" t="inlineStr">
         <is>
           <t>503540790</t>
@@ -62575,22 +63519,38 @@
         </is>
       </c>
       <c r="H941" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I941" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J941" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K941" t="inlineStr"/>
-      <c r="L941" t="inlineStr"/>
-      <c r="M941" t="inlineStr"/>
-      <c r="N941" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K941" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/dinnia-diaz-159a2a31|80</t>
+        </is>
+      </c>
+      <c r="L941" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M941" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N941" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O941" t="inlineStr">
         <is>
           <t>503540790</t>
@@ -62687,15 +63647,15 @@
       </c>
       <c r="G943" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://www.linkedin.com/in/daniela-martinez-isu</t>
         </is>
       </c>
       <c r="H943" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I943" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J943" t="inlineStr">
@@ -62703,10 +63663,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K943" t="inlineStr"/>
-      <c r="L943" t="inlineStr"/>
-      <c r="M943" t="inlineStr"/>
-      <c r="N943" t="inlineStr"/>
+      <c r="K943" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daniela-martinez-isu|80 ; https://cr.linkedin.com/in/mar%C3%ADa-mart%C3%ADnez-154485161|80 ; https://pa.linkedin.com/in/maria-martinez-8bb67b138|80</t>
+        </is>
+      </c>
+      <c r="L943" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M943" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N943" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O943" t="inlineStr">
         <is>
           <t>503550082</t>
@@ -63093,15 +64069,15 @@
       </c>
       <c r="G950" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://www.linkedin.com/in/mario-sanchez-aa0a4538/es</t>
         </is>
       </c>
       <c r="H950" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I950" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J950" t="inlineStr">
@@ -63109,10 +64085,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K950" t="inlineStr"/>
-      <c r="L950" t="inlineStr"/>
-      <c r="M950" t="inlineStr"/>
-      <c r="N950" t="inlineStr"/>
+      <c r="K950" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mario-sanchez-aa0a4538/es|80 ; https://cr.linkedin.com/in/mario-sanchez-a81665184|80 ; https://mx.linkedin.com/in/mario-sanchez-lopez-670a3452?trk=public_profile_browsemap_profile-result-card_result-card_full-click|80</t>
+        </is>
+      </c>
+      <c r="L950" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M950" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N950" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O950" t="inlineStr">
         <is>
           <t>503550827</t>
@@ -63209,15 +64201,15 @@
       </c>
       <c r="G952" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://pa.linkedin.com/in/katherine-castillo-78b9a427b</t>
         </is>
       </c>
       <c r="H952" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I952" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J952" t="inlineStr">
@@ -63225,10 +64217,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K952" t="inlineStr"/>
-      <c r="L952" t="inlineStr"/>
-      <c r="M952" t="inlineStr"/>
-      <c r="N952" t="inlineStr"/>
+      <c r="K952" t="inlineStr">
+        <is>
+          <t>https://pa.linkedin.com/in/katherine-castillo-78b9a427b|80 ; https://pa.linkedin.com/in/katherine-castillo-9a9053269|80 ; https://pe.linkedin.com/in/katherine-avila-castillo-591437b8|80</t>
+        </is>
+      </c>
+      <c r="L952" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M952" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N952" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O952" t="inlineStr">
         <is>
           <t>503550991</t>
@@ -63271,22 +64279,38 @@
         </is>
       </c>
       <c r="H953" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I953" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J953" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K953" t="inlineStr"/>
-      <c r="L953" t="inlineStr"/>
-      <c r="M953" t="inlineStr"/>
-      <c r="N953" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K953" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/maria-salazar-9832221a7|80 ; https://cr.linkedin.com/in/maria-salazar-7b06639b|80 ; https://www.linkedin.com/in/maria-salazar-780b58148|80</t>
+        </is>
+      </c>
+      <c r="L953" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M953" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N953" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O953" t="inlineStr">
         <is>
           <t>503560086</t>
@@ -63329,11 +64353,11 @@
         </is>
       </c>
       <c r="H954" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="I954" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J954" t="inlineStr">
@@ -63341,10 +64365,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K954" t="inlineStr"/>
-      <c r="L954" t="inlineStr"/>
-      <c r="M954" t="inlineStr"/>
-      <c r="N954" t="inlineStr"/>
+      <c r="K954" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/maria-salazar-castro-2233b734|86 ; https://cr.linkedin.com/in/maria-salazar-9832221a7|80 ; https://cr.linkedin.com/in/maria-salazar-7b06639b|80</t>
+        </is>
+      </c>
+      <c r="L954" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M954" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N954" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O954" t="inlineStr">
         <is>
           <t>503560086</t>
@@ -63383,26 +64423,42 @@
       </c>
       <c r="G955" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://www.linkedin.com/in/ana-morales-smith-27971a159</t>
         </is>
       </c>
       <c r="H955" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I955" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J955" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K955" t="inlineStr"/>
-      <c r="L955" t="inlineStr"/>
-      <c r="M955" t="inlineStr"/>
-      <c r="N955" t="inlineStr"/>
+          <t>ESTUDIÓ</t>
+        </is>
+      </c>
+      <c r="K955" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ana-morales-smith-27971a159|80 ; https://pa.linkedin.com/in/ana-morales-43757a51|80</t>
+        </is>
+      </c>
+      <c r="L955" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M955" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N955" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O955" t="inlineStr">
         <is>
           <t>503560110</t>
@@ -63441,15 +64497,15 @@
       </c>
       <c r="G956" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/patricia-rodr%C3%ADguez-691364131</t>
         </is>
       </c>
       <c r="H956" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I956" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J956" t="inlineStr">
@@ -63457,10 +64513,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K956" t="inlineStr"/>
-      <c r="L956" t="inlineStr"/>
-      <c r="M956" t="inlineStr"/>
-      <c r="N956" t="inlineStr"/>
+      <c r="K956" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/patricia-rodr%C3%ADguez-691364131|80 ; https://mx.linkedin.com/in/patricia-rodriguez-3272a417a|80 ; https://www.linkedin.com/in/patricia-rodriguez-cardenas-09103b147|80</t>
+        </is>
+      </c>
+      <c r="L956" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M956" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N956" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O956" t="inlineStr">
         <is>
           <t>503560174</t>
@@ -63499,15 +64571,15 @@
       </c>
       <c r="G957" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://mx.linkedin.com/in/jessica-hern%C3%A1ndez-l%C3%B3pez-584728208</t>
         </is>
       </c>
       <c r="H957" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I957" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J957" t="inlineStr">
@@ -63515,10 +64587,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K957" t="inlineStr"/>
-      <c r="L957" t="inlineStr"/>
-      <c r="M957" t="inlineStr"/>
-      <c r="N957" t="inlineStr"/>
+      <c r="K957" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/in/mar%C3%ADa-hern%C3%A1ndez-s%C3%A1nchez-614b6674|92 ; https://mx.linkedin.com/in/jessica-hern%C3%A1ndez-l%C3%B3pez-584728208|80 ; https://pa.linkedin.com/in/mar%C3%ADa-hernandez-736391252|80</t>
+        </is>
+      </c>
+      <c r="L957" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M957" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N957" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O957" t="inlineStr">
         <is>
           <t>503560272</t>
@@ -63615,15 +64703,15 @@
       </c>
       <c r="G959" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/diana-villegas-cascante-19985892</t>
         </is>
       </c>
       <c r="H959" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I959" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J959" t="inlineStr">
@@ -63631,10 +64719,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K959" t="inlineStr"/>
-      <c r="L959" t="inlineStr"/>
-      <c r="M959" t="inlineStr"/>
-      <c r="N959" t="inlineStr"/>
+      <c r="K959" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/diana-villegas-cascante-19985892|100</t>
+        </is>
+      </c>
+      <c r="L959" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M959" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N959" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O959" t="inlineStr">
         <is>
           <t>503560394</t>
@@ -63673,15 +64777,15 @@
       </c>
       <c r="G960" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/luis-salazar-177559b4/en</t>
         </is>
       </c>
       <c r="H960" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I960" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J960" t="inlineStr">
@@ -63689,10 +64793,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K960" t="inlineStr"/>
-      <c r="L960" t="inlineStr"/>
-      <c r="M960" t="inlineStr"/>
-      <c r="N960" t="inlineStr"/>
+      <c r="K960" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/luis-salazar-177559b4/en|80 ; https://cr.linkedin.com/in/luis-salazar-510523152|80 ; https://cr.linkedin.com/in/luis-j-salazar-p%C3%A9rez-6550962a3/es|80</t>
+        </is>
+      </c>
+      <c r="L960" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M960" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N960" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O960" t="inlineStr">
         <is>
           <t>503560595</t>
@@ -63731,15 +64851,15 @@
       </c>
       <c r="G961" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/yerling-rodriguez-ruiz-90672726</t>
         </is>
       </c>
       <c r="H961" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I961" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J961" t="inlineStr">
@@ -63747,10 +64867,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K961" t="inlineStr"/>
-      <c r="L961" t="inlineStr"/>
-      <c r="M961" t="inlineStr"/>
-      <c r="N961" t="inlineStr"/>
+      <c r="K961" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/yerling-rodriguez-ruiz-90672726|100</t>
+        </is>
+      </c>
+      <c r="L961" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M961" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N961" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O961" t="inlineStr">
         <is>
           <t>503560652</t>
@@ -63789,15 +64925,15 @@
       </c>
       <c r="G962" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/eunice-rodriguez-9a0396239</t>
         </is>
       </c>
       <c r="H962" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I962" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J962" t="inlineStr">
@@ -63805,10 +64941,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K962" t="inlineStr"/>
-      <c r="L962" t="inlineStr"/>
-      <c r="M962" t="inlineStr"/>
-      <c r="N962" t="inlineStr"/>
+      <c r="K962" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/eunice-rodriguez-9a0396239|80</t>
+        </is>
+      </c>
+      <c r="L962" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M962" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N962" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O962" t="inlineStr">
         <is>
           <t>503560759</t>
@@ -63905,15 +65057,15 @@
       </c>
       <c r="G964" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/giovanni-torres-rodr%C3%ADguez-8833a4186</t>
         </is>
       </c>
       <c r="H964" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I964" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J964" t="inlineStr">
@@ -63921,10 +65073,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K964" t="inlineStr"/>
-      <c r="L964" t="inlineStr"/>
-      <c r="M964" t="inlineStr"/>
-      <c r="N964" t="inlineStr"/>
+      <c r="K964" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/giovanni-torres-rodr%C3%ADguez-8833a4186|100</t>
+        </is>
+      </c>
+      <c r="L964" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M964" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N964" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O964" t="inlineStr">
         <is>
           <t>503560809</t>
@@ -63963,15 +65131,15 @@
       </c>
       <c r="G965" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/mar%C3%ADa-jos%C3%A9-quir%C3%B3s-561260212</t>
         </is>
       </c>
       <c r="H965" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I965" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J965" t="inlineStr">
@@ -63979,10 +65147,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K965" t="inlineStr"/>
-      <c r="L965" t="inlineStr"/>
-      <c r="M965" t="inlineStr"/>
-      <c r="N965" t="inlineStr"/>
+      <c r="K965" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/mar%C3%ADa-jos%C3%A9-quir%C3%B3s-561260212|80</t>
+        </is>
+      </c>
+      <c r="L965" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M965" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N965" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O965" t="inlineStr">
         <is>
           <t>503560843</t>
@@ -64137,15 +65321,15 @@
       </c>
       <c r="G968" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://mx.linkedin.com/in/eduardo-venegas-20abba9a</t>
         </is>
       </c>
       <c r="H968" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I968" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J968" t="inlineStr">
@@ -64153,10 +65337,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K968" t="inlineStr"/>
-      <c r="L968" t="inlineStr"/>
-      <c r="M968" t="inlineStr"/>
-      <c r="N968" t="inlineStr"/>
+      <c r="K968" t="inlineStr">
+        <is>
+          <t>https://mx.linkedin.com/in/eduardo-venegas-20abba9a|80 ; https://cr.linkedin.com/in/jose-venegas-a444a3186|80 ; https://cr.linkedin.com/in/jose-venegas-271775a7|80</t>
+        </is>
+      </c>
+      <c r="L968" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M968" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N968" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O968" t="inlineStr">
         <is>
           <t>503560922</t>
@@ -64427,15 +65627,15 @@
       </c>
       <c r="G973" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/kevin-alonso-murillo-rojas-4083a3136</t>
         </is>
       </c>
       <c r="H973" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I973" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J973" t="inlineStr">
@@ -64443,10 +65643,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K973" t="inlineStr"/>
-      <c r="L973" t="inlineStr"/>
-      <c r="M973" t="inlineStr"/>
-      <c r="N973" t="inlineStr"/>
+      <c r="K973" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/kevin-alonso-murillo-rojas-4083a3136|100 ; https://cr.linkedin.com/in/luis-alonso-brice%C3%B1o-murillo-965117190|90 ; https://co.linkedin.com/in/luis-efren-murillo-78776967|83</t>
+        </is>
+      </c>
+      <c r="L973" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M973" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N973" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O973" t="inlineStr">
         <is>
           <t>503570116</t>
@@ -64485,15 +65701,15 @@
       </c>
       <c r="G974" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/jose-villegas-20194484</t>
         </is>
       </c>
       <c r="H974" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I974" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J974" t="inlineStr">
@@ -64501,10 +65717,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K974" t="inlineStr"/>
-      <c r="L974" t="inlineStr"/>
-      <c r="M974" t="inlineStr"/>
-      <c r="N974" t="inlineStr"/>
+      <c r="K974" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/jose-villegas-20194484|80</t>
+        </is>
+      </c>
+      <c r="L974" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M974" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N974" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O974" t="inlineStr">
         <is>
           <t>503570159</t>
@@ -64547,11 +65779,11 @@
         </is>
       </c>
       <c r="H975" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I975" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J975" t="inlineStr">
@@ -64559,10 +65791,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K975" t="inlineStr"/>
-      <c r="L975" t="inlineStr"/>
-      <c r="M975" t="inlineStr"/>
-      <c r="N975" t="inlineStr"/>
+      <c r="K975" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/jose-villegas-20194484|80</t>
+        </is>
+      </c>
+      <c r="L975" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M975" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N975" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O975" t="inlineStr">
         <is>
           <t>503570159</t>
@@ -64601,26 +65849,42 @@
       </c>
       <c r="G976" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://pa.linkedin.com/in/c%C3%A9sar-medina-091456295</t>
         </is>
       </c>
       <c r="H976" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I976" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J976" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K976" t="inlineStr"/>
-      <c r="L976" t="inlineStr"/>
-      <c r="M976" t="inlineStr"/>
-      <c r="N976" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K976" t="inlineStr">
+        <is>
+          <t>https://pa.linkedin.com/in/c%C3%A9sar-medina-091456295|100</t>
+        </is>
+      </c>
+      <c r="L976" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M976" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N976" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O976" t="inlineStr">
         <is>
           <t>503570228</t>
@@ -64663,22 +65927,38 @@
         </is>
       </c>
       <c r="H977" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I977" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J977" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K977" t="inlineStr"/>
-      <c r="L977" t="inlineStr"/>
-      <c r="M977" t="inlineStr"/>
-      <c r="N977" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K977" t="inlineStr">
+        <is>
+          <t>https://pa.linkedin.com/in/c%C3%A9sar-medina-091456295|100</t>
+        </is>
+      </c>
+      <c r="L977" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M977" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N977" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O977" t="inlineStr">
         <is>
           <t>503570228</t>
@@ -64717,15 +65997,15 @@
       </c>
       <c r="G978" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/jose-leal-palma</t>
         </is>
       </c>
       <c r="H978" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="I978" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J978" t="inlineStr">
@@ -64733,10 +66013,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K978" t="inlineStr"/>
-      <c r="L978" t="inlineStr"/>
-      <c r="M978" t="inlineStr"/>
-      <c r="N978" t="inlineStr"/>
+      <c r="K978" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/jose-leal-palma|83</t>
+        </is>
+      </c>
+      <c r="L978" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M978" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N978" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O978" t="inlineStr">
         <is>
           <t>503570353</t>
@@ -64837,22 +66133,38 @@
         </is>
       </c>
       <c r="H980" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I980" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J980" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K980" t="inlineStr"/>
-      <c r="L980" t="inlineStr"/>
-      <c r="M980" t="inlineStr"/>
-      <c r="N980" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K980" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/maria-salazar-9832221a7|80 ; https://cr.linkedin.com/in/maria-salazar-7b06639b|80 ; https://www.linkedin.com/in/maria-salazar-780b58148|80</t>
+        </is>
+      </c>
+      <c r="L980" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M980" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N980" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O980" t="inlineStr">
         <is>
           <t>503570673</t>
@@ -64891,26 +66203,42 @@
       </c>
       <c r="G981" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/ennio-cubillo-perez-27aa17201</t>
         </is>
       </c>
       <c r="H981" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I981" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J981" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K981" t="inlineStr"/>
-      <c r="L981" t="inlineStr"/>
-      <c r="M981" t="inlineStr"/>
-      <c r="N981" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K981" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/ennio-cubillo-perez-27aa17201|100</t>
+        </is>
+      </c>
+      <c r="L981" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M981" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N981" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O981" t="inlineStr">
         <is>
           <t>503570695</t>
@@ -64953,22 +66281,38 @@
         </is>
       </c>
       <c r="H982" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I982" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J982" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K982" t="inlineStr"/>
-      <c r="L982" t="inlineStr"/>
-      <c r="M982" t="inlineStr"/>
-      <c r="N982" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K982" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/ennio-cubillo-perez-27aa17201|100</t>
+        </is>
+      </c>
+      <c r="L982" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M982" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N982" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O982" t="inlineStr">
         <is>
           <t>503570695</t>
@@ -65007,15 +66351,15 @@
       </c>
       <c r="G983" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/solange-guti%C3%A9rrez-quesada-307a17192</t>
         </is>
       </c>
       <c r="H983" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I983" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J983" t="inlineStr">
@@ -65023,10 +66367,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K983" t="inlineStr"/>
-      <c r="L983" t="inlineStr"/>
-      <c r="M983" t="inlineStr"/>
-      <c r="N983" t="inlineStr"/>
+      <c r="K983" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/solange-guti%C3%A9rrez-quesada-307a17192|80</t>
+        </is>
+      </c>
+      <c r="L983" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M983" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N983" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O983" t="inlineStr">
         <is>
           <t>503570765</t>
@@ -65065,15 +66425,15 @@
       </c>
       <c r="G984" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/cesar-murillo-205133200</t>
         </is>
       </c>
       <c r="H984" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I984" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J984" t="inlineStr">
@@ -65081,10 +66441,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K984" t="inlineStr"/>
-      <c r="L984" t="inlineStr"/>
-      <c r="M984" t="inlineStr"/>
-      <c r="N984" t="inlineStr"/>
+      <c r="K984" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/cesar-murillo-205133200|80 ; https://cr.linkedin.com/in/alfonso-murillo-santacruz-63257a15|80 ; https://mx.linkedin.com/in/alfonso-murillo-flores-05a861239|60</t>
+        </is>
+      </c>
+      <c r="L984" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M984" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N984" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O984" t="inlineStr">
         <is>
           <t>503570799</t>
@@ -65127,11 +66503,11 @@
         </is>
       </c>
       <c r="H985" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I985" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J985" t="inlineStr">
@@ -65139,10 +66515,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K985" t="inlineStr"/>
-      <c r="L985" t="inlineStr"/>
-      <c r="M985" t="inlineStr"/>
-      <c r="N985" t="inlineStr"/>
+      <c r="K985" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/cesar-murillo-205133200|80 ; https://cr.linkedin.com/in/alfonso-murillo-santacruz-63257a15|80 ; https://mx.linkedin.com/in/alfonso-murillo-flores-05a861239|60</t>
+        </is>
+      </c>
+      <c r="L985" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M985" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N985" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O985" t="inlineStr">
         <is>
           <t>503570799</t>
@@ -65181,15 +66573,15 @@
       </c>
       <c r="G986" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/andrey-contreras-557b0582</t>
         </is>
       </c>
       <c r="H986" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I986" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J986" t="inlineStr">
@@ -65197,10 +66589,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K986" t="inlineStr"/>
-      <c r="L986" t="inlineStr"/>
-      <c r="M986" t="inlineStr"/>
-      <c r="N986" t="inlineStr"/>
+      <c r="K986" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/andrey-contreras-557b0582|80 ; https://pa.linkedin.com/in/h-orlando-contreras-810230321|80</t>
+        </is>
+      </c>
+      <c r="L986" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M986" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N986" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O986" t="inlineStr">
         <is>
           <t>503570806</t>
@@ -65243,11 +66651,11 @@
         </is>
       </c>
       <c r="H987" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I987" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J987" t="inlineStr">
@@ -65255,10 +66663,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K987" t="inlineStr"/>
-      <c r="L987" t="inlineStr"/>
-      <c r="M987" t="inlineStr"/>
-      <c r="N987" t="inlineStr"/>
+      <c r="K987" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/andrey-contreras-557b0582|80 ; https://pa.linkedin.com/in/h-orlando-contreras-810230321|80</t>
+        </is>
+      </c>
+      <c r="L987" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M987" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N987" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O987" t="inlineStr">
         <is>
           <t>503570806</t>
@@ -65297,15 +66721,15 @@
       </c>
       <c r="G988" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/diana-acosta-baltodano-b4aa6028</t>
         </is>
       </c>
       <c r="H988" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I988" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J988" t="inlineStr">
@@ -65313,10 +66737,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K988" t="inlineStr"/>
-      <c r="L988" t="inlineStr"/>
-      <c r="M988" t="inlineStr"/>
-      <c r="N988" t="inlineStr"/>
+      <c r="K988" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/diana-acosta-baltodano-b4aa6028|100 ; https://pa.linkedin.com/in/diana-acosta-7853b9369|80 ; https://cr.linkedin.com/in/diana-acosta-73667461|80</t>
+        </is>
+      </c>
+      <c r="L988" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M988" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N988" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O988" t="inlineStr">
         <is>
           <t>503570823</t>
@@ -65529,15 +66969,15 @@
       </c>
       <c r="G992" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/marcia-espinoza-441879102</t>
         </is>
       </c>
       <c r="H992" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I992" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J992" t="inlineStr">
@@ -65545,10 +66985,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K992" t="inlineStr"/>
-      <c r="L992" t="inlineStr"/>
-      <c r="M992" t="inlineStr"/>
-      <c r="N992" t="inlineStr"/>
+      <c r="K992" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/marcia-espinoza-441879102|80 ; https://cr.linkedin.com/in/marcia-espinoza-rios-a78634183|80</t>
+        </is>
+      </c>
+      <c r="L992" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M992" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N992" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O992" t="inlineStr">
         <is>
           <t>503580237</t>
@@ -65591,11 +67047,11 @@
         </is>
       </c>
       <c r="H993" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I993" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J993" t="inlineStr">
@@ -65603,10 +67059,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K993" t="inlineStr"/>
-      <c r="L993" t="inlineStr"/>
-      <c r="M993" t="inlineStr"/>
-      <c r="N993" t="inlineStr"/>
+      <c r="K993" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/marcia-espinoza-441879102|80 ; https://cr.linkedin.com/in/marcia-espinoza-rios-a78634183|80</t>
+        </is>
+      </c>
+      <c r="L993" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M993" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N993" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O993" t="inlineStr">
         <is>
           <t>503580237</t>
@@ -65645,15 +67117,15 @@
       </c>
       <c r="G994" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://www.linkedin.com/in/mercedes-duarte-23b612250</t>
         </is>
       </c>
       <c r="H994" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I994" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J994" t="inlineStr">
@@ -65661,10 +67133,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K994" t="inlineStr"/>
-      <c r="L994" t="inlineStr"/>
-      <c r="M994" t="inlineStr"/>
-      <c r="N994" t="inlineStr"/>
+      <c r="K994" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mercedes-duarte-23b612250|80</t>
+        </is>
+      </c>
+      <c r="L994" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M994" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N994" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O994" t="inlineStr">
         <is>
           <t>503580264</t>
@@ -65761,15 +67249,15 @@
       </c>
       <c r="G996" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/isabel-villalobos-221ab8384</t>
         </is>
       </c>
       <c r="H996" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I996" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J996" t="inlineStr">
@@ -65777,10 +67265,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K996" t="inlineStr"/>
-      <c r="L996" t="inlineStr"/>
-      <c r="M996" t="inlineStr"/>
-      <c r="N996" t="inlineStr"/>
+      <c r="K996" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/isabel-villalobos-221ab8384|80 ; https://pe.linkedin.com/in/isabel-villalobos-a5761921b|80</t>
+        </is>
+      </c>
+      <c r="L996" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M996" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N996" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O996" t="inlineStr">
         <is>
           <t>503580383</t>
@@ -65819,15 +67323,15 @@
       </c>
       <c r="G997" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/silvia-chaves-rodriguez-a3a602274</t>
         </is>
       </c>
       <c r="H997" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I997" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J997" t="inlineStr">
@@ -65835,10 +67339,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K997" t="inlineStr"/>
-      <c r="L997" t="inlineStr"/>
-      <c r="M997" t="inlineStr"/>
-      <c r="N997" t="inlineStr"/>
+      <c r="K997" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/silvia-chaves-rodriguez-a3a602274|100 ; https://cr.linkedin.com/in/silvia-rodriguez-16288b5|80 ; https://www.linkedin.com/in/silvia-rodriguez-franquiz|80</t>
+        </is>
+      </c>
+      <c r="L997" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M997" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N997" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O997" t="inlineStr">
         <is>
           <t>503580437</t>
@@ -65877,26 +67397,42 @@
       </c>
       <c r="G998" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/lilliam-campos-2b6735179</t>
         </is>
       </c>
       <c r="H998" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I998" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J998" t="inlineStr">
         <is>
-          <t>NO DETERMINADO</t>
-        </is>
-      </c>
-      <c r="K998" t="inlineStr"/>
-      <c r="L998" t="inlineStr"/>
-      <c r="M998" t="inlineStr"/>
-      <c r="N998" t="inlineStr"/>
+          <t>ESTUDIA</t>
+        </is>
+      </c>
+      <c r="K998" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/lilliam-campos-2b6735179|80 ; https://cr.linkedin.com/in/maria-campos-5a874437b|80 ; https://cr.linkedin.com/in/maria-campos-8b1259148|80</t>
+        </is>
+      </c>
+      <c r="L998" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M998" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N998" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O998" t="inlineStr">
         <is>
           <t>503580467</t>
@@ -66051,15 +67587,15 @@
       </c>
       <c r="G1001" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>https://cr.linkedin.com/in/gerardo-antonio-l%C3%B3pez-chaves-a54557203</t>
         </is>
       </c>
       <c r="H1001" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I1001" t="inlineStr">
         <is>
-          <t>NO_ENCONTRADO</t>
+          <t>REVISAR</t>
         </is>
       </c>
       <c r="J1001" t="inlineStr">
@@ -66067,10 +67603,26 @@
           <t>NO DETERMINADO</t>
         </is>
       </c>
-      <c r="K1001" t="inlineStr"/>
-      <c r="L1001" t="inlineStr"/>
-      <c r="M1001" t="inlineStr"/>
-      <c r="N1001" t="inlineStr"/>
+      <c r="K1001" t="inlineStr">
+        <is>
+          <t>https://cr.linkedin.com/in/gerardo-antonio-l%C3%B3pez-chaves-a54557203|90 ; https://cr.linkedin.com/in/gerardo-lopez-020285b6|80 ; https://pa.linkedin.com/in/gerardo-lopez-4a064a116|80</t>
+        </is>
+      </c>
+      <c r="L1001" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M1001" t="inlineStr">
+        <is>
+          <t>NO/DUDOSO</t>
+        </is>
+      </c>
+      <c r="N1001" t="inlineStr">
+        <is>
+          <t>SIN INFO</t>
+        </is>
+      </c>
       <c r="O1001" t="inlineStr">
         <is>
           <t>503580585</t>
